--- a/Geographic_Maps_plotting/stations_type_B.xlsx
+++ b/Geographic_Maps_plotting/stations_type_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding projects\seismology\Geographic_Maps_plotting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D948B5DA-42E0-4CE3-98DB-0602FE3CDAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA4E77D-3FF0-4FB9-964C-3EF3A331E473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,9 +75,6 @@
     <t>EL OUED</t>
   </si>
   <si>
-    <t>7.4</t>
-  </si>
-  <si>
     <t>36.8</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>7.5</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1081,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -1098,172 +1098,172 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
